--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T06:07:01+00:00</t>
+    <t>2024-10-25T08:29:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:29:24+00:00</t>
+    <t>2024-10-29T09:40:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -451,23 +451,23 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>CoverageEligibilityResponse.extension:EndOfEligibility</t>
-  </si>
-  <si>
-    <t>EndOfEligibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-EndOfEligibility}
+    <t>CoverageEligibilityResponse.extension:fristende</t>
+  </si>
+  <si>
+    <t>fristende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-fristende}
 </t>
   </si>
   <si>
     <t>"Fristende"</t>
   </si>
   <si>
-    <t>CoverageEligibilityResponse.extension:VAEStatus</t>
-  </si>
-  <si>
-    <t>VAEStatus</t>
+    <t>CoverageEligibilityResponse.extension:vaeStatus</t>
+  </si>
+  <si>
+    <t>vaeStatus</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-vaestatus}
@@ -477,26 +477,26 @@
     <t>"VAEST - Status der Versichertenanspruchserklärung"</t>
   </si>
   <si>
-    <t>CoverageEligibilityResponse.extension:MealCostExcemption</t>
-  </si>
-  <si>
-    <t>MealCostExcemption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-MealCostExcemption}
+    <t>CoverageEligibilityResponse.extension:verpflegskostenBeitragsbefreiung</t>
+  </si>
+  <si>
+    <t>verpflegskostenBeitragsbefreiung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verpflegskostenBeitragsbefreiung}
 </t>
   </si>
   <si>
     <t>"VKBEFR – Verpflegskosten-Beitragsbefreiung"</t>
   </si>
   <si>
-    <t>CoverageEligibilityResponse.extension:NumberOfPreviouslyPaidDays</t>
-  </si>
-  <si>
-    <t>NumberOfPreviouslyPaidDays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-NumberOfPreviouslyPaidDays}
+    <t>CoverageEligibilityResponse.extension:vortageanzahlAufKostenbeitrag</t>
+  </si>
+  <si>
+    <t>vortageanzahlAufKostenbeitrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-vortageanzahlAufKostenbeitrag}
 </t>
   </si>
   <si>
@@ -1635,9 +1635,9 @@
   <dimension ref="A1:AN70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="65.5703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="68.3359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="65.5703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="32.1484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1645,7 +1645,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="86.765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="90.52734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:40:57+00:00</t>
+    <t>2024-10-29T10:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
